--- a/Happy_Hatch_Trading_System/Happy_Hatch_Data/Happy_Hatch_Trading_Inventory_Data.xlsx
+++ b/Happy_Hatch_Trading_System/Happy_Hatch_Data/Happy_Hatch_Trading_Inventory_Data.xlsx
@@ -454,22 +454,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,50 +504,45 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Available Specifications</t>
+          <t>Available Colours</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Available Colours</t>
+          <t>In Stock</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>In Stock</t>
+          <t>Onboard Price</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Onboard Price</t>
+          <t>Profitability Percentage</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Profitability Percentage</t>
+          <t>Net Price</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Net Price</t>
+          <t>Market Price</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Market Price</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Photo File</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Photo File</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -564,27 +559,27 @@
           <t>AIR Blower</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="E5">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A5)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A5)</f>
         <v/>
       </c>
-      <c r="G5" s="4">
+      <c r="F5" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A5,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A5)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A5)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I5" s="4">
-        <f>G5*(1+H5)</f>
-        <v/>
-      </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4">
-        <f>I5-G5</f>
-        <v/>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="H5" s="4">
+        <f>F5*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4">
+        <f>H5-F5</f>
+        <v/>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Product_Photos/HH101.jpg</t>
         </is>
@@ -601,27 +596,27 @@
           <t>AITOS Whisk</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="E6">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A6)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A6)</f>
         <v/>
       </c>
-      <c r="G6" s="4">
+      <c r="F6" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A6,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A6)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A6)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I6" s="4">
-        <f>G6*(1+H6)</f>
-        <v/>
-      </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4">
-        <f>I6-G6</f>
-        <v/>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="H6" s="4">
+        <f>F6*(1+G6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4">
+        <f>H6-F6</f>
+        <v/>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Product_Photos/HH102.jpg</t>
         </is>
@@ -638,27 +633,27 @@
           <t>Artificial Plant</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="E7">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A7)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A7)</f>
         <v/>
       </c>
-      <c r="G7" s="4">
+      <c r="F7" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A7,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A7)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A7)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I7" s="4">
-        <f>G7*(1+H7)</f>
-        <v/>
-      </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4">
-        <f>I7-G7</f>
-        <v/>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="H7" s="4">
+        <f>F7*(1+G7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4">
+        <f>H7-F7</f>
+        <v/>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Product_Photos/HH103.jpg</t>
         </is>
@@ -672,30 +667,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BDO: Storage box Lengthy - Blue</t>
-        </is>
-      </c>
-      <c r="F8">
+          <t>BDO: Storage box Lengthy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Blue, Pink, White</t>
+        </is>
+      </c>
+      <c r="E8">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A8)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A8)</f>
         <v/>
       </c>
-      <c r="G8" s="4">
+      <c r="F8" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A8,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A8)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A8)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I8" s="4">
-        <f>G8*(1+H8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4">
-        <f>I8-G8</f>
-        <v/>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="H8" s="4">
+        <f>F8*(1+G8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4">
+        <f>H8-F8</f>
+        <v/>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Product_Photos/HH104.jpg</t>
         </is>
@@ -709,30 +709,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BDO: Storage box Lengthy - Pink</t>
-        </is>
-      </c>
-      <c r="F9">
+          <t>BDO: Storage box Wide</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Blue, Pink, White</t>
+        </is>
+      </c>
+      <c r="E9">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A9)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A9)</f>
         <v/>
       </c>
-      <c r="G9" s="4">
+      <c r="F9" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A9,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A9)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A9)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I9" s="4">
-        <f>G9*(1+H9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4">
-        <f>I9-G9</f>
-        <v/>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="H9" s="4">
+        <f>F9*(1+G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4">
+        <f>H9-F9</f>
+        <v/>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Product_Photos/HH105.jpg</t>
         </is>
@@ -746,30 +751,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BDO: Storage box Lengthy - White</t>
-        </is>
-      </c>
-      <c r="F10">
+          <t>BDO: Wave pattern toilet brush</t>
+        </is>
+      </c>
+      <c r="E10">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A10)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A10)</f>
         <v/>
       </c>
-      <c r="G10" s="4">
+      <c r="F10" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A10,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A10)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A10)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I10" s="4">
-        <f>G10*(1+H10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4">
-        <f>I10-G10</f>
-        <v/>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="H10" s="4">
+        <f>F10*(1+G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4">
+        <f>H10-F10</f>
+        <v/>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Product_Photos/HH106.jpg</t>
         </is>
@@ -783,30 +788,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BDO: Storage box Wide - Blue</t>
-        </is>
-      </c>
-      <c r="F11">
+          <t>Big Basket - White</t>
+        </is>
+      </c>
+      <c r="E11">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A11)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A11)</f>
         <v/>
       </c>
-      <c r="G11" s="4">
+      <c r="F11" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A11,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A11)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A11)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I11" s="4">
-        <f>G11*(1+H11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4">
-        <f>I11-G11</f>
-        <v/>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="H11" s="4">
+        <f>F11*(1+G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4">
+        <f>H11-F11</f>
+        <v/>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Product_Photos/HH107.jpg</t>
         </is>
@@ -820,30 +825,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BDO: Storage box Wide - Pink</t>
-        </is>
-      </c>
-      <c r="F12">
+          <t>Cheese knife</t>
+        </is>
+      </c>
+      <c r="E12">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A12)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A12)</f>
         <v/>
       </c>
-      <c r="G12" s="4">
+      <c r="F12" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A12,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A12)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A12)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I12" s="4">
-        <f>G12*(1+H12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4">
-        <f>I12-G12</f>
-        <v/>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="H12" s="4">
+        <f>F12*(1+G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4">
+        <f>H12-F12</f>
+        <v/>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Product_Photos/HH108.jpg</t>
         </is>
@@ -857,30 +862,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BDO: Storage box Wide - White</t>
-        </is>
-      </c>
-      <c r="F13">
+          <t>Cleaning cloth</t>
+        </is>
+      </c>
+      <c r="E13">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A13)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A13)</f>
         <v/>
       </c>
-      <c r="G13" s="4">
+      <c r="F13" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A13,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A13)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A13)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I13" s="4">
-        <f>G13*(1+H13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4">
-        <f>I13-G13</f>
-        <v/>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="H13" s="4">
+        <f>F13*(1+G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4">
+        <f>H13-F13</f>
+        <v/>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Product_Photos/HH109.jpg</t>
         </is>
@@ -894,30 +899,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BDO: Wave pattern toilet brush</t>
-        </is>
-      </c>
-      <c r="F14">
+          <t>Clip</t>
+        </is>
+      </c>
+      <c r="E14">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A14)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A14)</f>
         <v/>
       </c>
-      <c r="G14" s="4">
+      <c r="F14" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A14,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A14)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A14)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I14" s="4">
-        <f>G14*(1+H14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4">
-        <f>I14-G14</f>
-        <v/>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="H14" s="4">
+        <f>F14*(1+G14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4">
+        <f>H14-F14</f>
+        <v/>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Product_Photos/HH110.jpg</t>
         </is>
@@ -931,30 +936,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Big Basket - White</t>
-        </is>
-      </c>
-      <c r="F15">
+          <t>Contay - Mini utensil set</t>
+        </is>
+      </c>
+      <c r="E15">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A15)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A15)</f>
         <v/>
       </c>
-      <c r="G15" s="4">
+      <c r="F15" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A15,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A15)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A15)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I15" s="4">
-        <f>G15*(1+H15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4">
-        <f>I15-G15</f>
-        <v/>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="H15" s="4">
+        <f>F15*(1+G15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4">
+        <f>H15-F15</f>
+        <v/>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Product_Photos/HH111.jpg</t>
         </is>
@@ -968,30 +973,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cheese knife</t>
-        </is>
-      </c>
-      <c r="F16">
+          <t>Cooling towel</t>
+        </is>
+      </c>
+      <c r="E16">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A16)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A16)</f>
         <v/>
       </c>
-      <c r="G16" s="4">
+      <c r="F16" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A16,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A16)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A16)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I16" s="4">
-        <f>G16*(1+H16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4">
-        <f>I16-G16</f>
-        <v/>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="H16" s="4">
+        <f>F16*(1+G16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4">
+        <f>H16-F16</f>
+        <v/>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Product_Photos/HH112.jpg</t>
         </is>
@@ -1005,30 +1010,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cleaning cloth</t>
-        </is>
-      </c>
-      <c r="F17">
+          <t>Crunches</t>
+        </is>
+      </c>
+      <c r="E17">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A17)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A17)</f>
         <v/>
       </c>
-      <c r="G17" s="4">
+      <c r="F17" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A17,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A17)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A17)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I17" s="4">
-        <f>G17*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4">
-        <f>I17-G17</f>
-        <v/>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="H17" s="4">
+        <f>F17*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4">
+        <f>H17-F17</f>
+        <v/>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Product_Photos/HH113.jpg</t>
         </is>
@@ -1042,30 +1047,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clip</t>
-        </is>
-      </c>
-      <c r="F18">
+          <t>Cup Holder</t>
+        </is>
+      </c>
+      <c r="E18">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A18)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A18)</f>
         <v/>
       </c>
-      <c r="G18" s="4">
+      <c r="F18" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A18,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A18)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A18)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I18" s="4">
-        <f>G18*(1+H18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4">
-        <f>I18-G18</f>
-        <v/>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="H18" s="4">
+        <f>F18*(1+G18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4">
+        <f>H18-F18</f>
+        <v/>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Product_Photos/HH114.jpg</t>
         </is>
@@ -1079,30 +1084,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Contay - Mini utensil set</t>
-        </is>
-      </c>
-      <c r="F19">
+          <t>DEX - Brush</t>
+        </is>
+      </c>
+      <c r="E19">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A19)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A19)</f>
         <v/>
       </c>
-      <c r="G19" s="4">
+      <c r="F19" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A19,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A19)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A19)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I19" s="4">
-        <f>G19*(1+H19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4">
-        <f>I19-G19</f>
-        <v/>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="H19" s="4">
+        <f>F19*(1+G19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4">
+        <f>H19-F19</f>
+        <v/>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Product_Photos/HH115.jpg</t>
         </is>
@@ -1116,30 +1121,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cooling towel</t>
-        </is>
-      </c>
-      <c r="F20">
+          <t>Egg cutter</t>
+        </is>
+      </c>
+      <c r="E20">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A20)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A20)</f>
         <v/>
       </c>
-      <c r="G20" s="4">
+      <c r="F20" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A20,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A20)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A20)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="G20" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I20" s="4">
-        <f>G20*(1+H20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4">
-        <f>I20-G20</f>
-        <v/>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="H20" s="4">
+        <f>F20*(1+G20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4">
+        <f>H20-F20</f>
+        <v/>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Product_Photos/HH116.jpg</t>
         </is>
@@ -1153,30 +1158,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crunches</t>
-        </is>
-      </c>
-      <c r="F21">
+          <t>Eye mask</t>
+        </is>
+      </c>
+      <c r="E21">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A21)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A21)</f>
         <v/>
       </c>
-      <c r="G21" s="4">
+      <c r="F21" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A21,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A21)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A21)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="G21" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I21" s="4">
-        <f>G21*(1+H21)</f>
-        <v/>
-      </c>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4">
-        <f>I21-G21</f>
-        <v/>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="H21" s="4">
+        <f>F21*(1+G21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4">
+        <f>H21-F21</f>
+        <v/>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Product_Photos/HH117.jpg</t>
         </is>
@@ -1190,30 +1195,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cup Holder</t>
-        </is>
-      </c>
-      <c r="F22">
+          <t>Folding Rack</t>
+        </is>
+      </c>
+      <c r="E22">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A22)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A22)</f>
         <v/>
       </c>
-      <c r="G22" s="4">
+      <c r="F22" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A22,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A22)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A22)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I22" s="4">
-        <f>G22*(1+H22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4">
-        <f>I22-G22</f>
-        <v/>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="H22" s="4">
+        <f>F22*(1+G22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4">
+        <f>H22-F22</f>
+        <v/>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Product_Photos/HH118.jpg</t>
         </is>
@@ -1227,30 +1232,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DEX - Brush</t>
-        </is>
-      </c>
-      <c r="F23">
+          <t>Foot pad for washing machine</t>
+        </is>
+      </c>
+      <c r="E23">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A23)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A23)</f>
         <v/>
       </c>
-      <c r="G23" s="4">
+      <c r="F23" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A23,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A23)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A23)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I23" s="4">
-        <f>G23*(1+H23)</f>
-        <v/>
-      </c>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4">
-        <f>I23-G23</f>
-        <v/>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="H23" s="4">
+        <f>F23*(1+G23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4">
+        <f>H23-F23</f>
+        <v/>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Product_Photos/HH119.jpg</t>
         </is>
@@ -1264,30 +1269,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Egg cutter</t>
-        </is>
-      </c>
-      <c r="F24">
+          <t>Fridge storage bag</t>
+        </is>
+      </c>
+      <c r="E24">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A24)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A24)</f>
         <v/>
       </c>
-      <c r="G24" s="4">
+      <c r="F24" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A24,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A24)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A24)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="G24" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I24" s="4">
-        <f>G24*(1+H24)</f>
-        <v/>
-      </c>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4">
-        <f>I24-G24</f>
-        <v/>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="H24" s="4">
+        <f>F24*(1+G24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4">
+        <f>H24-F24</f>
+        <v/>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Product_Photos/HH120.jpg</t>
         </is>
@@ -1301,30 +1306,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Eye mask</t>
-        </is>
-      </c>
-      <c r="F25">
+          <t>Fun 4 pencil shaped pen holder</t>
+        </is>
+      </c>
+      <c r="E25">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A25)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A25)</f>
         <v/>
       </c>
-      <c r="G25" s="4">
+      <c r="F25" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A25,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A25)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A25)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="G25" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I25" s="4">
-        <f>G25*(1+H25)</f>
-        <v/>
-      </c>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4">
-        <f>I25-G25</f>
-        <v/>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="H25" s="4">
+        <f>F25*(1+G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4">
+        <f>H25-F25</f>
+        <v/>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Product_Photos/HH121.jpg</t>
         </is>
@@ -1338,30 +1343,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Folding Rack</t>
-        </is>
-      </c>
-      <c r="F26">
+          <t>Gap cleaning brush</t>
+        </is>
+      </c>
+      <c r="E26">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A26)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A26)</f>
         <v/>
       </c>
-      <c r="G26" s="4">
+      <c r="F26" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A26,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A26)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A26)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="G26" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I26" s="4">
-        <f>G26*(1+H26)</f>
-        <v/>
-      </c>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4">
-        <f>I26-G26</f>
-        <v/>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="H26" s="4">
+        <f>F26*(1+G26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4">
+        <f>H26-F26</f>
+        <v/>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Product_Photos/HH122.jpg</t>
         </is>
@@ -1375,30 +1380,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Foot pad for washing machine</t>
-        </is>
-      </c>
-      <c r="F27">
+          <t>Garlic grater</t>
+        </is>
+      </c>
+      <c r="E27">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A27)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A27)</f>
         <v/>
       </c>
-      <c r="G27" s="4">
+      <c r="F27" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A27,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A27)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A27)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="G27" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I27" s="4">
-        <f>G27*(1+H27)</f>
-        <v/>
-      </c>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4">
-        <f>I27-G27</f>
-        <v/>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="H27" s="4">
+        <f>F27*(1+G27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4">
+        <f>H27-F27</f>
+        <v/>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Product_Photos/HH123.jpg</t>
         </is>
@@ -1412,30 +1417,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fridge storage bag</t>
-        </is>
-      </c>
-      <c r="F28">
+          <t>Hole-free wall mounted wall storage rack</t>
+        </is>
+      </c>
+      <c r="E28">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A28)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A28)</f>
         <v/>
       </c>
-      <c r="G28" s="4">
+      <c r="F28" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A28,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A28)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A28)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="G28" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I28" s="4">
-        <f>G28*(1+H28)</f>
-        <v/>
-      </c>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4">
-        <f>I28-G28</f>
-        <v/>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="H28" s="4">
+        <f>F28*(1+G28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4">
+        <f>H28-F28</f>
+        <v/>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Product_Photos/HH124.jpg</t>
         </is>
@@ -1449,30 +1454,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fun 4 pencil shaped pen holder</t>
-        </is>
-      </c>
-      <c r="F29">
+          <t>Jig saw puzzle</t>
+        </is>
+      </c>
+      <c r="E29">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A29)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A29)</f>
         <v/>
       </c>
-      <c r="G29" s="4">
+      <c r="F29" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A29,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A29)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A29)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="G29" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I29" s="4">
-        <f>G29*(1+H29)</f>
-        <v/>
-      </c>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4">
-        <f>I29-G29</f>
-        <v/>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="H29" s="4">
+        <f>F29*(1+G29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4">
+        <f>H29-F29</f>
+        <v/>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Product_Photos/HH125.jpg</t>
         </is>
@@ -1486,30 +1491,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gap cleaning brush</t>
-        </is>
-      </c>
-      <c r="F30">
+          <t>Maxtop shoulder massager</t>
+        </is>
+      </c>
+      <c r="E30">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A30)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A30)</f>
         <v/>
       </c>
-      <c r="G30" s="4">
+      <c r="F30" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A30,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A30)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A30)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="G30" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I30" s="4">
-        <f>G30*(1+H30)</f>
-        <v/>
-      </c>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4">
-        <f>I30-G30</f>
-        <v/>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="H30" s="4">
+        <f>F30*(1+G30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4">
+        <f>H30-F30</f>
+        <v/>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Product_Photos/HH126.jpg</t>
         </is>
@@ -1523,30 +1528,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Garlic grater</t>
-        </is>
-      </c>
-      <c r="F31">
+          <t>Mengmengabi cute rabbit bottle</t>
+        </is>
+      </c>
+      <c r="E31">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A31)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A31)</f>
         <v/>
       </c>
-      <c r="G31" s="4">
+      <c r="F31" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A31,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A31)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A31)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="G31" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I31" s="4">
-        <f>G31*(1+H31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4">
-        <f>I31-G31</f>
-        <v/>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="H31" s="4">
+        <f>F31*(1+G31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4">
+        <f>H31-F31</f>
+        <v/>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Product_Photos/HH127.jpg</t>
         </is>
@@ -1560,30 +1565,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hole-free wall mounted wall storage rack</t>
-        </is>
-      </c>
-      <c r="F32">
+          <t>Mesh tray</t>
+        </is>
+      </c>
+      <c r="E32">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A32)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A32)</f>
         <v/>
       </c>
-      <c r="G32" s="4">
+      <c r="F32" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A32,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A32)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A32)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="G32" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I32" s="4">
-        <f>G32*(1+H32)</f>
-        <v/>
-      </c>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4">
-        <f>I32-G32</f>
-        <v/>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="H32" s="4">
+        <f>F32*(1+G32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4">
+        <f>H32-F32</f>
+        <v/>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Product_Photos/HH128.jpg</t>
         </is>
@@ -1597,30 +1602,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jig saw puzzle</t>
-        </is>
-      </c>
-      <c r="F33">
+          <t>Muscle massager</t>
+        </is>
+      </c>
+      <c r="E33">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A33)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A33)</f>
         <v/>
       </c>
-      <c r="G33" s="4">
+      <c r="F33" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A33,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A33)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A33)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="G33" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I33" s="4">
-        <f>G33*(1+H33)</f>
-        <v/>
-      </c>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4">
-        <f>I33-G33</f>
-        <v/>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="H33" s="4">
+        <f>F33*(1+G33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4">
+        <f>H33-F33</f>
+        <v/>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Product_Photos/HH129.jpg</t>
         </is>
@@ -1634,30 +1639,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Maxtop shoulder massager</t>
-        </is>
-      </c>
-      <c r="F34">
+          <t>NICE Bottle</t>
+        </is>
+      </c>
+      <c r="E34">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A34)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A34)</f>
         <v/>
       </c>
-      <c r="G34" s="4">
+      <c r="F34" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A34,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A34)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A34)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="G34" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I34" s="4">
-        <f>G34*(1+H34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4">
-        <f>I34-G34</f>
-        <v/>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="H34" s="4">
+        <f>F34*(1+G34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4">
+        <f>H34-F34</f>
+        <v/>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Product_Photos/HH130.jpg</t>
         </is>
@@ -1671,30 +1676,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mengmengabi cute rabbit bottle</t>
-        </is>
-      </c>
-      <c r="F35">
+          <t>Peeler - P</t>
+        </is>
+      </c>
+      <c r="E35">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A35)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A35)</f>
         <v/>
       </c>
-      <c r="G35" s="4">
+      <c r="F35" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A35,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A35)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A35)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="G35" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I35" s="4">
-        <f>G35*(1+H35)</f>
-        <v/>
-      </c>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4">
-        <f>I35-G35</f>
-        <v/>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="H35" s="4">
+        <f>F35*(1+G35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4">
+        <f>H35-F35</f>
+        <v/>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Product_Photos/HH131.jpg</t>
         </is>
@@ -1708,30 +1713,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mesh tray</t>
-        </is>
-      </c>
-      <c r="F36">
+          <t>Peeler - Y</t>
+        </is>
+      </c>
+      <c r="E36">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A36)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A36)</f>
         <v/>
       </c>
-      <c r="G36" s="4">
+      <c r="F36" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A36,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A36)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A36)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="G36" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I36" s="4">
-        <f>G36*(1+H36)</f>
-        <v/>
-      </c>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4">
-        <f>I36-G36</f>
-        <v/>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="H36" s="4">
+        <f>F36*(1+G36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4">
+        <f>H36-F36</f>
+        <v/>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Product_Photos/HH132.jpg</t>
         </is>
@@ -1745,30 +1750,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Muscle massager</t>
-        </is>
-      </c>
-      <c r="F37">
+          <t>Portable Sealing Machine</t>
+        </is>
+      </c>
+      <c r="E37">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A37)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A37)</f>
         <v/>
       </c>
-      <c r="G37" s="4">
+      <c r="F37" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A37,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A37)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A37)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="G37" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I37" s="4">
-        <f>G37*(1+H37)</f>
-        <v/>
-      </c>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4">
-        <f>I37-G37</f>
-        <v/>
-      </c>
-      <c r="L37" t="inlineStr">
+      <c r="H37" s="4">
+        <f>F37*(1+G37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4">
+        <f>H37-F37</f>
+        <v/>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Product_Photos/HH133.jpg</t>
         </is>
@@ -1782,30 +1787,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NICE Bottle</t>
-        </is>
-      </c>
-      <c r="F38">
+          <t>Push toy</t>
+        </is>
+      </c>
+      <c r="E38">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A38)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A38)</f>
         <v/>
       </c>
-      <c r="G38" s="4">
+      <c r="F38" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A38,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A38)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A38)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="G38" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I38" s="4">
-        <f>G38*(1+H38)</f>
-        <v/>
-      </c>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4">
-        <f>I38-G38</f>
-        <v/>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="H38" s="4">
+        <f>F38*(1+G38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4">
+        <f>H38-F38</f>
+        <v/>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Product_Photos/HH134.jpg</t>
         </is>
@@ -1819,30 +1824,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Peeler - P</t>
-        </is>
-      </c>
-      <c r="F39">
+          <t>Rolling Chair</t>
+        </is>
+      </c>
+      <c r="E39">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A39)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A39)</f>
         <v/>
       </c>
-      <c r="G39" s="4">
+      <c r="F39" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A39,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A39)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A39)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="G39" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I39" s="4">
-        <f>G39*(1+H39)</f>
-        <v/>
-      </c>
-      <c r="J39" s="4" t="n"/>
-      <c r="K39" s="4">
-        <f>I39-G39</f>
-        <v/>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="H39" s="4">
+        <f>F39*(1+G39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4">
+        <f>H39-F39</f>
+        <v/>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Product_Photos/HH135.jpg</t>
         </is>
@@ -1856,30 +1861,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Peeler - Y</t>
-        </is>
-      </c>
-      <c r="F40">
+          <t>Scalp massager</t>
+        </is>
+      </c>
+      <c r="E40">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A40)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A40)</f>
         <v/>
       </c>
-      <c r="G40" s="4">
+      <c r="F40" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A40,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A40)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A40)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="G40" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I40" s="4">
-        <f>G40*(1+H40)</f>
-        <v/>
-      </c>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4">
-        <f>I40-G40</f>
-        <v/>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="H40" s="4">
+        <f>F40*(1+G40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4">
+        <f>H40-F40</f>
+        <v/>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Product_Photos/HH136.jpg</t>
         </is>
@@ -1893,30 +1898,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Portable Sealing Machine</t>
-        </is>
-      </c>
-      <c r="F41">
+          <t>School bag</t>
+        </is>
+      </c>
+      <c r="E41">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A41)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A41)</f>
         <v/>
       </c>
-      <c r="G41" s="4">
+      <c r="F41" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A41,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A41)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A41)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="G41" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I41" s="4">
-        <f>G41*(1+H41)</f>
-        <v/>
-      </c>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4">
-        <f>I41-G41</f>
-        <v/>
-      </c>
-      <c r="L41" t="inlineStr">
+      <c r="H41" s="4">
+        <f>F41*(1+G41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4">
+        <f>H41-F41</f>
+        <v/>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Product_Photos/HH137.jpg</t>
         </is>
@@ -1930,30 +1935,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Push toy</t>
-        </is>
-      </c>
-      <c r="F42">
+          <t>Stanley cup</t>
+        </is>
+      </c>
+      <c r="E42">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A42)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A42)</f>
         <v/>
       </c>
-      <c r="G42" s="4">
+      <c r="F42" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A42,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A42)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A42)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="G42" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I42" s="4">
-        <f>G42*(1+H42)</f>
-        <v/>
-      </c>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4">
-        <f>I42-G42</f>
-        <v/>
-      </c>
-      <c r="L42" t="inlineStr">
+      <c r="H42" s="4">
+        <f>F42*(1+G42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4">
+        <f>H42-F42</f>
+        <v/>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Product_Photos/HH138.jpg</t>
         </is>
@@ -1967,30 +1972,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rolling Chair</t>
-        </is>
-      </c>
-      <c r="F43">
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E43">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A43)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A43)</f>
         <v/>
       </c>
-      <c r="G43" s="4">
+      <c r="F43" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A43,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A43)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A43)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="G43" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I43" s="4">
-        <f>G43*(1+H43)</f>
-        <v/>
-      </c>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4">
-        <f>I43-G43</f>
-        <v/>
-      </c>
-      <c r="L43" t="inlineStr">
+      <c r="H43" s="4">
+        <f>F43*(1+G43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4">
+        <f>H43-F43</f>
+        <v/>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Product_Photos/HH139.jpg</t>
         </is>
@@ -2004,30 +2009,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Scalp massager</t>
-        </is>
-      </c>
-      <c r="F44">
+          <t>Toothpick Dispenser - Cartoon</t>
+        </is>
+      </c>
+      <c r="E44">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A44)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A44)</f>
         <v/>
       </c>
-      <c r="G44" s="4">
+      <c r="F44" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A44,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A44)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A44)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="G44" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I44" s="4">
-        <f>G44*(1+H44)</f>
-        <v/>
-      </c>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4">
-        <f>I44-G44</f>
-        <v/>
-      </c>
-      <c r="L44" t="inlineStr">
+      <c r="H44" s="4">
+        <f>F44*(1+G44)</f>
+        <v/>
+      </c>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4">
+        <f>H44-F44</f>
+        <v/>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Product_Photos/HH140.jpg</t>
         </is>
@@ -2041,30 +2046,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>School bag</t>
-        </is>
-      </c>
-      <c r="F45">
+          <t>Two bottle holding bag</t>
+        </is>
+      </c>
+      <c r="E45">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A45)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A45)</f>
         <v/>
       </c>
-      <c r="G45" s="4">
+      <c r="F45" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A45,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A45)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A45)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="G45" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I45" s="4">
-        <f>G45*(1+H45)</f>
-        <v/>
-      </c>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4">
-        <f>I45-G45</f>
-        <v/>
-      </c>
-      <c r="L45" t="inlineStr">
+      <c r="H45" s="4">
+        <f>F45*(1+G45)</f>
+        <v/>
+      </c>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4">
+        <f>H45-F45</f>
+        <v/>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Product_Photos/HH141.jpg</t>
         </is>
@@ -2078,182 +2083,62 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stanley cup</t>
-        </is>
-      </c>
-      <c r="F46">
+          <t>White plastic basket</t>
+        </is>
+      </c>
+      <c r="E46">
         <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A46)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A46)</f>
         <v/>
       </c>
-      <c r="G46" s="4">
+      <c r="F46" s="4">
         <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A46,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A46)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A46)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
         <v/>
       </c>
-      <c r="H46" s="5" t="n">
+      <c r="G46" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I46" s="4">
-        <f>G46*(1+H46)</f>
-        <v/>
-      </c>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4">
-        <f>I46-G46</f>
-        <v/>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="H46" s="4">
+        <f>F46*(1+G46)</f>
+        <v/>
+      </c>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4">
+        <f>H46-F46</f>
+        <v/>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Product_Photos/HH142.jpg</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>HH143</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="F47">
-        <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A47)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A47)</f>
-        <v/>
-      </c>
-      <c r="G47" s="4">
-        <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A47,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A47)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A47)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
-        <v/>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I47" s="4">
-        <f>G47*(1+H47)</f>
-        <v/>
-      </c>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4">
-        <f>I47-G47</f>
-        <v/>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Product_Photos/HH143.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>HH144</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Toothpick Dispenser - Cartoon</t>
-        </is>
-      </c>
-      <c r="F48">
-        <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A48)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A48)</f>
-        <v/>
-      </c>
-      <c r="G48" s="4">
-        <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A48,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A48)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A48)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
-        <v/>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I48" s="4">
-        <f>G48*(1+H48)</f>
-        <v/>
-      </c>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4">
-        <f>I48-G48</f>
-        <v/>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Product_Photos/HH144.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>HH145</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Two bottle holding bag</t>
-        </is>
-      </c>
-      <c r="F49">
-        <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A49)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A49)</f>
-        <v/>
-      </c>
-      <c r="G49" s="4">
-        <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A49,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A49)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A49)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
-        <v/>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I49" s="4">
-        <f>G49*(1+H49)</f>
-        <v/>
-      </c>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4">
-        <f>I49-G49</f>
-        <v/>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Product_Photos/HH145.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>HH146</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>White plastic basket</t>
-        </is>
-      </c>
-      <c r="F50">
-        <f>SUMIFS(PURCHASE!$E$5:$E$2000,PURCHASE!$C$5:$C$2000,A50)-SUMIFS(SALES_ITEMS!$G$5:$G$2000,SALES_ITEMS!$C$5:$C$2000,A50)</f>
-        <v/>
-      </c>
-      <c r="G50" s="4">
-        <f>IF(COUNTIFS(PURCHASE!$C$5:$C$2000,A50,PURCHASE!$E$5:$E$2000,"&gt;0")=0,0,IFERROR(LOOKUP(2,1/((PURCHASE!$C$5:$C$2000=A50)*(PURCHASE!$E$5:$E$2000&gt;0)*(PURCHASE!$B$5:$B$2000=SUMPRODUCT(MAX((PURCHASE!$C$5:$C$2000=A50)*(PURCHASE!$E$5:$E$2000&gt;0)*PURCHASE!$B$5:$B$2000)))),PURCHASE!$L$5:$L$2000),0))</f>
-        <v/>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I50" s="4">
-        <f>G50*(1+H50)</f>
-        <v/>
-      </c>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4">
-        <f>I50-G50</f>
-        <v/>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Product_Photos/HH146.jpg</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2376,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2462,7 +2347,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2861,7 +2745,7 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2872,7 +2756,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
@@ -2916,7 +2800,7 @@
         <v/>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2927,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
@@ -2971,7 +2855,7 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2982,7 +2866,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
@@ -3026,7 +2910,7 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3037,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
@@ -3081,7 +2965,7 @@
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3092,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
@@ -3136,7 +3020,7 @@
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3147,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
@@ -3191,18 +3075,18 @@
         <v/>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
@@ -3356,18 +3240,18 @@
         <v/>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
@@ -3411,18 +3295,18 @@
         <v/>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
@@ -3466,7 +3350,7 @@
         <v/>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3477,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
@@ -3521,7 +3405,7 @@
         <v/>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3532,7 +3416,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
@@ -3576,18 +3460,18 @@
         <v/>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
@@ -3631,7 +3515,7 @@
         <v/>
       </c>
       <c r="E22" t="n">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3642,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
@@ -3741,7 +3625,7 @@
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3752,7 +3636,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
@@ -3796,7 +3680,7 @@
         <v/>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3807,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
@@ -3851,7 +3735,7 @@
         <v/>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3862,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
@@ -4016,7 +3900,7 @@
         <v/>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4027,7 +3911,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
@@ -4071,7 +3955,7 @@
         <v/>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4082,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
@@ -4126,7 +4010,7 @@
         <v/>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4137,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
@@ -4181,7 +4065,7 @@
         <v/>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4192,7 +4076,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
@@ -4236,7 +4120,7 @@
         <v/>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4247,7 +4131,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
@@ -4291,7 +4175,7 @@
         <v/>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
@@ -4346,7 +4230,7 @@
         <v/>
       </c>
       <c r="E35" t="n">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4357,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="n"/>
@@ -4401,7 +4285,7 @@
         <v/>
       </c>
       <c r="E36" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4412,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
@@ -4456,7 +4340,7 @@
         <v/>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
@@ -4511,7 +4395,7 @@
         <v/>
       </c>
       <c r="E38" t="n">
-        <v>44</v>
+        <v>240</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4522,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>44</v>
+        <v>240</v>
       </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
@@ -4566,7 +4450,7 @@
         <v/>
       </c>
       <c r="E39" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4577,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
@@ -4621,7 +4505,7 @@
         <v/>
       </c>
       <c r="E40" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4632,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
@@ -4731,7 +4615,7 @@
         <v/>
       </c>
       <c r="E42" t="n">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4742,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
@@ -4841,7 +4725,7 @@
         <v/>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4852,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
@@ -4896,7 +4780,7 @@
         <v/>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4907,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
@@ -4951,7 +4835,7 @@
         <v/>
       </c>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4962,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
@@ -4988,224 +4872,40 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>PUR-043</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>HH143</t>
-        </is>
-      </c>
-      <c r="D47">
-        <f>IFERROR(INDEX(PRODUCTS!$B$5:$B$2000,MATCH(C47,PRODUCTS!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="B47" s="7" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4">
-        <f>H47+I47+J47</f>
-        <v/>
-      </c>
-      <c r="L47" s="4">
-        <f>IF(E47&gt;0,K47/E47,0)</f>
-        <v/>
-      </c>
-      <c r="N47">
-        <f>IFERROR(INDEX(SHIPPER!$B$5:$B$2000,MATCH(M47,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="O47">
-        <f>IFERROR(INDEX(SHIPPER!$D$5:$D$2000,MATCH(M47,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="P47">
-        <f>IFERROR(INDEX(SHIPPER!$E$5:$E$2000,MATCH(M47,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>PUR-044</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>HH144</t>
-        </is>
-      </c>
-      <c r="D48">
-        <f>IFERROR(INDEX(PRODUCTS!$B$5:$B$2000,MATCH(C48,PRODUCTS!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E48" t="n">
-        <v>12</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>12</v>
-      </c>
+      <c r="B48" s="7" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4">
-        <f>H48+I48+J48</f>
-        <v/>
-      </c>
-      <c r="L48" s="4">
-        <f>IF(E48&gt;0,K48/E48,0)</f>
-        <v/>
-      </c>
-      <c r="N48">
-        <f>IFERROR(INDEX(SHIPPER!$B$5:$B$2000,MATCH(M48,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="O48">
-        <f>IFERROR(INDEX(SHIPPER!$D$5:$D$2000,MATCH(M48,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="P48">
-        <f>IFERROR(INDEX(SHIPPER!$E$5:$E$2000,MATCH(M48,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>PUR-045</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>HH145</t>
-        </is>
-      </c>
-      <c r="D49">
-        <f>IFERROR(INDEX(PRODUCTS!$B$5:$B$2000,MATCH(C49,PRODUCTS!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B49" s="7" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4">
-        <f>H49+I49+J49</f>
-        <v/>
-      </c>
-      <c r="L49" s="4">
-        <f>IF(E49&gt;0,K49/E49,0)</f>
-        <v/>
-      </c>
-      <c r="N49">
-        <f>IFERROR(INDEX(SHIPPER!$B$5:$B$2000,MATCH(M49,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="O49">
-        <f>IFERROR(INDEX(SHIPPER!$D$5:$D$2000,MATCH(M49,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="P49">
-        <f>IFERROR(INDEX(SHIPPER!$E$5:$E$2000,MATCH(M49,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>PUR-046</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>HH146</t>
-        </is>
-      </c>
-      <c r="D50">
-        <f>IFERROR(INDEX(PRODUCTS!$B$5:$B$2000,MATCH(C50,PRODUCTS!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E50" t="n">
-        <v>6</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="B50" s="7" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4">
-        <f>H50+I50+J50</f>
-        <v/>
-      </c>
-      <c r="L50" s="4">
-        <f>IF(E50&gt;0,K50/E50,0)</f>
-        <v/>
-      </c>
-      <c r="N50">
-        <f>IFERROR(INDEX(SHIPPER!$B$5:$B$2000,MATCH(M50,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="O50">
-        <f>IFERROR(INDEX(SHIPPER!$D$5:$D$2000,MATCH(M50,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
-      <c r="P50">
-        <f>IFERROR(INDEX(SHIPPER!$E$5:$E$2000,MATCH(M50,SHIPPER!$A$5:$A$2000,0)),"")</f>
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
